--- a/jogos_2025-04-08.xlsx
+++ b/jogos_2025-04-08.xlsx
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,16 +1675,16 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -1693,7 +1693,7 @@
         <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
         <v>3.25</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V10" t="n">
         <v>1.06</v>
       </c>
       <c r="W10" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['29', '45', '46', '90+3']</t>
+          <t>['15', '23']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45755.54166666666</v>
@@ -1794,35 +1794,35 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>1.05</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>22.49</v>
       </c>
       <c r="O11" t="n">
-        <v>2.95</v>
+        <v>1.36</v>
       </c>
       <c r="P11" t="n">
-        <v>1.98</v>
+        <v>3.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.6</v>
+        <v>11.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="T11" t="n">
-        <v>3.25</v>
+        <v>1.75</v>
       </c>
       <c r="U11" t="n">
-        <v>1.28</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.06</v>
       </c>
-      <c r="W11" t="n">
-        <v>1.39</v>
-      </c>
       <c r="X11" t="n">
-        <v>2.59</v>
+        <v>8.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.36</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.62</v>
       </c>
-      <c r="AA11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['15', '23']</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>['87']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.57</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.73</v>
+        <v>1.13</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.3</v>
+        <v>6</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45755.54166666666</v>
@@ -2052,32 +2052,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.05</v>
+        <v>2.64</v>
       </c>
       <c r="M13" t="n">
-        <v>9</v>
+        <v>3.19</v>
       </c>
       <c r="N13" t="n">
-        <v>22.49</v>
+        <v>2.64</v>
       </c>
       <c r="O13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.36</v>
       </c>
-      <c r="P13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.06</v>
-      </c>
       <c r="X13" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.8</v>
+        <v>1.61</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.65</v>
+        <v>3.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.15</v>
+        <v>1.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>['29', '45', '46', '90+3']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['87']</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.05</v>
+        <v>1.48</v>
       </c>
       <c r="AH13" t="n">
-        <v>8.960000000000001</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.13</v>
+        <v>2.1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45755.54166666666</v>
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
         <v>2</v>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['9']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['13', '64']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI15" t="n">
         <v>1.82</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['39', '49']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>2.53</v>
+        <v>2.1</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45755.58333333334</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Hannover 96 II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.23</v>
+        <v>3.42</v>
       </c>
       <c r="N16" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="O16" t="n">
-        <v>3.78</v>
+        <v>3.62</v>
       </c>
       <c r="P16" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S16" t="n">
-        <v>2.65</v>
+        <v>2.93</v>
       </c>
       <c r="T16" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="U16" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['76']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.32</v>
       </c>
-      <c r="X16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['62', '76']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['35', '44']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AI16" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45755.58333333334</v>
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>3.73</v>
       </c>
       <c r="N17" t="n">
-        <v>4.9</v>
+        <v>4.13</v>
       </c>
       <c r="O17" t="n">
-        <v>2.14</v>
+        <v>2.31</v>
       </c>
       <c r="P17" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="R17" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="T17" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="U17" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="V17" t="n">
         <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X17" t="n">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['39', '49']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.92</v>
       </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['2', '7', '68', '72']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['15', '86']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2.16</v>
-      </c>
       <c r="AI17" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45755.58333333334</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hannover 96 II</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2851,10 +2851,10 @@
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.4</v>
+        <v>1.46</v>
       </c>
       <c r="M19" t="n">
-        <v>3.42</v>
+        <v>4.7</v>
       </c>
       <c r="N19" t="n">
-        <v>2.13</v>
+        <v>5.7</v>
       </c>
       <c r="O19" t="n">
-        <v>3.62</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.09</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.76</v>
+        <v>5.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>2.93</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="U19" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
-        <v>3.48</v>
+        <v>4.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.6</v>
+        <v>1.14</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.32</v>
+        <v>2.4</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.15</v>
+        <v>1.48</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.76</v>
+        <v>3</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45755.58333333334</v>
@@ -2955,32 +2955,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['2', '7', '68', '72']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['15', '86']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AI20" t="n">
         <v>1.46</v>
       </c>
-      <c r="M20" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['29']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['14']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AJ20" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45755.58333333334</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.34</v>
+        <v>3.18</v>
       </c>
       <c r="M21" t="n">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="N21" t="n">
-        <v>3.01</v>
+        <v>2.26</v>
       </c>
       <c r="O21" t="n">
-        <v>2.88</v>
+        <v>3.78</v>
       </c>
       <c r="P21" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.58</v>
+        <v>2.78</v>
       </c>
       <c r="R21" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="T21" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="U21" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="V21" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="X21" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.14</v>
+        <v>3.62</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>['62', '76']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['13', '64']</t>
+          <t>['35', '44']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="AI21" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>1.82</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45755.58333333334</v>
@@ -3471,35 +3471,35 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
         <v>3</v>
       </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
       <c r="I24" t="n">
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.4</v>
+        <v>2.34</v>
       </c>
       <c r="M24" t="n">
-        <v>4.2</v>
+        <v>3.38</v>
       </c>
       <c r="N24" t="n">
-        <v>6</v>
+        <v>2.88</v>
       </c>
       <c r="O24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['3', '62']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['39', '54', '69']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>2.25</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>['44', '65', '90+1']</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['54']</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>3.6</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45755.65625</v>
@@ -3729,32 +3729,32 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="M26" t="n">
-        <v>3.36</v>
+        <v>4.2</v>
       </c>
       <c r="N26" t="n">
-        <v>1.79</v>
+        <v>6</v>
       </c>
       <c r="O26" t="n">
-        <v>5</v>
+        <v>2.25</v>
       </c>
       <c r="P26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC26" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AD26" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['44', '65', '90+1']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.8</v>
+        <v>1.36</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.67</v>
+        <v>3.6</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45755.65625</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,22 +3868,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
         <v>2</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>2</v>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.2</v>
+        <v>2.74</v>
       </c>
       <c r="M27" t="n">
-        <v>3.99</v>
+        <v>3.29</v>
       </c>
       <c r="N27" t="n">
-        <v>1.72</v>
+        <v>2.49</v>
       </c>
       <c r="O27" t="n">
-        <v>4.65</v>
+        <v>3.1</v>
       </c>
       <c r="P27" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.21</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="T27" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W27" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="X27" t="n">
-        <v>4.15</v>
+        <v>3.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.53</v>
+        <v>3.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['22']</t>
+          <t>['51', '85']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['19', '37']</t>
+          <t>['16', '38']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>2.17</v>
+        <v>1.42</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.69</v>
+        <v>1.95</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45755.65625</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,16 +3997,16 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="M28" t="n">
-        <v>3.76</v>
+        <v>3.47</v>
       </c>
       <c r="N28" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="O28" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="P28" t="n">
         <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="T28" t="n">
         <v>3</v>
       </c>
       <c r="U28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W28" t="n">
         <v>1.33</v>
       </c>
-      <c r="V28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.38</v>
-      </c>
       <c r="X28" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AA28" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC28" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['21']</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45755.65625</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.24</v>
+        <v>1.94</v>
       </c>
       <c r="M29" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="N29" t="n">
         <v>3.47</v>
       </c>
-      <c r="N29" t="n">
-        <v>2.98</v>
-      </c>
       <c r="O29" t="n">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="R29" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="S29" t="n">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="T29" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="U29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>['11']</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
         <v>1.3</v>
       </c>
-      <c r="V29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>['55']</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45755.65625</v>
@@ -4255,25 +4255,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="M30" t="n">
-        <v>3.47</v>
+        <v>3.39</v>
       </c>
       <c r="N30" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="O30" t="n">
-        <v>3.24</v>
+        <v>3.38</v>
       </c>
       <c r="P30" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.08</v>
+        <v>3.26</v>
       </c>
       <c r="R30" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U30" t="n">
         <v>1.31</v>
       </c>
-      <c r="S30" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.21</v>
       </c>
-      <c r="X30" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AC30" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.16</v>
+        <v>1.89</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['34', '53', '72']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AI30" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45755.65625</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,109 +4384,109 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>['34', '53', '72']</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI31" t="n">
         <v>2</v>
       </c>
-      <c r="H31" t="n">
-        <v>2</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="M31" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="O31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>['51', '85']</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>['16', '38']</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AJ31" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45755.65625</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.34</v>
+        <v>4.7</v>
       </c>
       <c r="M32" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="N32" t="n">
-        <v>2.88</v>
+        <v>1.79</v>
       </c>
       <c r="O32" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="P32" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="R32" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y32" t="n">
         <v>2.63</v>
       </c>
-      <c r="T32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X32" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.98</v>
-      </c>
       <c r="Z32" t="n">
-        <v>1.77</v>
+        <v>1.45</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.55</v>
+        <v>5.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['3', '62']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['39', '54', '69']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.38</v>
+        <v>1.85</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45755.65625</v>
@@ -4642,19 +4642,19 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="M33" t="n">
-        <v>3.37</v>
+        <v>3.47</v>
       </c>
       <c r="N33" t="n">
-        <v>2.98</v>
+        <v>2.78</v>
       </c>
       <c r="O33" t="n">
         <v>2.85</v>
       </c>
       <c r="P33" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="R33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U33" t="n">
         <v>1.42</v>
       </c>
-      <c r="S33" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB33" t="n">
         <v>1.35</v>
       </c>
-      <c r="V33" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AC33" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['56', '90+6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>['62']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AI33" t="n">
         <v>1.85</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45755.65625</v>
@@ -4771,19 +4771,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G34" t="n">
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="M34" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="N34" t="n">
-        <v>3.14</v>
+        <v>2.98</v>
       </c>
       <c r="O34" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="P34" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="R34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W34" t="n">
         <v>1.38</v>
       </c>
-      <c r="S34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.3</v>
-      </c>
       <c r="X34" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG34" t="n">
         <v>1.33</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AI34" t="n">
         <v>1.8</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45755.65625</v>
@@ -4900,19 +4900,19 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="M35" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>2.78</v>
+        <v>3.14</v>
       </c>
       <c r="O35" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="P35" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="R35" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S35" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="T35" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U35" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V35" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W35" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X35" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45755.65625</v>
@@ -5029,25 +5029,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="M36" t="n">
-        <v>3.29</v>
+        <v>3.99</v>
       </c>
       <c r="N36" t="n">
-        <v>2.8</v>
+        <v>1.72</v>
       </c>
       <c r="O36" t="n">
-        <v>3.08</v>
+        <v>4.65</v>
       </c>
       <c r="P36" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.48</v>
+        <v>2.21</v>
       </c>
       <c r="R36" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S36" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="T36" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="U36" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W36" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="X36" t="n">
-        <v>3.02</v>
+        <v>4.15</v>
       </c>
       <c r="Y36" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.48</v>
+        <v>2.53</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>['19', '37']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.43</v>
+        <v>2.17</v>
       </c>
       <c r="AH36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>2.15</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45755.65625</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,16 +5158,16 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
@@ -5176,7 +5176,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="N37" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>5</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S37" t="n">
         <v>2.62</v>
       </c>
-      <c r="M37" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="O37" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.67</v>
-      </c>
       <c r="T37" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V37" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W37" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="X37" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="Y37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC37" t="n">
         <v>2</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AD37" t="n">
         <v>1.73</v>
       </c>
-      <c r="AA37" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>['21']</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.46</v>
+        <v>2.05</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.04</v>
+        <v>1.57</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45755.65625</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,16 +5287,16 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
         <v>1</v>
@@ -5305,7 +5305,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.82</v>
+        <v>2.29</v>
       </c>
       <c r="M38" t="n">
-        <v>3.47</v>
+        <v>3.37</v>
       </c>
       <c r="N38" t="n">
-        <v>4.3</v>
+        <v>2.98</v>
       </c>
       <c r="O38" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="P38" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R38" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S38" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="T38" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U38" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V38" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W38" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X38" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AC38" t="n">
         <v>1.8</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['56', '90+6']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>['62']</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45755.65625</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5434,7 +5434,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.94</v>
+        <v>2.45</v>
       </c>
       <c r="M39" t="n">
-        <v>3.73</v>
+        <v>3.29</v>
       </c>
       <c r="N39" t="n">
-        <v>3.47</v>
+        <v>2.8</v>
       </c>
       <c r="O39" t="n">
-        <v>2.53</v>
+        <v>3.08</v>
       </c>
       <c r="P39" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.05</v>
+        <v>3.48</v>
       </c>
       <c r="R39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W39" t="n">
         <v>1.31</v>
       </c>
-      <c r="S39" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.22</v>
-      </c>
       <c r="X39" t="n">
-        <v>3.64</v>
+        <v>3.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.97</v>
+        <v>3.48</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5505,20 +5505,20 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.69</v>
+        <v>1.99</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45755.65625</v>
@@ -5545,25 +5545,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.39</v>
+        <v>1.85</v>
       </c>
       <c r="M40" t="n">
-        <v>3.57</v>
+        <v>3.71</v>
       </c>
       <c r="N40" t="n">
-        <v>2.98</v>
+        <v>4.5</v>
       </c>
       <c r="O40" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="R40" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S40" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="T40" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="U40" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V40" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W40" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="X40" t="n">
-        <v>2.85</v>
+        <v>3.55</v>
       </c>
       <c r="Y40" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.95</v>
       </c>
-      <c r="Z40" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>['58', '70', '75']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38', '88']</t>
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45755.66666666666</v>
@@ -5674,109 +5674,109 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P41" t="n">
         <v>2</v>
       </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="M41" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="N41" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O41" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q41" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="R41" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S41" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="T41" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U41" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V41" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W41" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="X41" t="n">
-        <v>3.55</v>
+        <v>2.85</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.25</v>
+        <v>2.17</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.33</v>
+        <v>1.69</v>
       </c>
       <c r="AC41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD41" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>['58', '70', '75']</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>['38', '88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45755.66666666666</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talleres Córdoba</t>
+          <t>Carabobo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5947,7 +5947,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.61</v>
+        <v>1.1</v>
       </c>
       <c r="M43" t="n">
-        <v>3.18</v>
+        <v>8.9</v>
       </c>
       <c r="N43" t="n">
-        <v>2.69</v>
+        <v>21</v>
       </c>
       <c r="O43" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="P43" t="n">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.4</v>
+        <v>13</v>
       </c>
       <c r="R43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U43" t="n">
         <v>1.62</v>
       </c>
-      <c r="S43" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T43" t="n">
-        <v>4</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.22</v>
-      </c>
       <c r="V43" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="W43" t="n">
-        <v>1.55</v>
+        <v>1.17</v>
       </c>
       <c r="X43" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="Z43" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD43" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA43" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AB43" t="n">
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>['88', '90+8']</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI43" t="n">
         <v>1.13</v>
       </c>
-      <c r="AC43" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>['9', '57']</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AJ43" t="n">
-        <v>1.83</v>
+        <v>6</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45755.79166666666</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Carabobo</t>
+          <t>Talleres Córdoba</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6076,7 +6076,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.1</v>
+        <v>2.61</v>
       </c>
       <c r="M44" t="n">
-        <v>8.9</v>
+        <v>3.18</v>
       </c>
       <c r="N44" t="n">
-        <v>21</v>
+        <v>2.69</v>
       </c>
       <c r="O44" t="n">
+        <v>4</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T44" t="n">
+        <v>4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z44" t="n">
         <v>1.5</v>
       </c>
-      <c r="P44" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>13</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S44" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X44" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2.47</v>
-      </c>
       <c r="AA44" t="n">
-        <v>1.95</v>
+        <v>5.75</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.7</v>
+        <v>1.13</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AD44" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>['9', '57']</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
         <v>1.5</v>
       </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>['88', '90+8']</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AH44" t="n">
-        <v>5</v>
+        <v>1.37</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.13</v>
+        <v>2.38</v>
       </c>
       <c r="AJ44" t="n">
-        <v>6</v>
+        <v>1.83</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45755.79166666666</v>
@@ -6319,25 +6319,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M46" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N46" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>6</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
         <v>1.36</v>
       </c>
-      <c r="M46" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="N46" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O46" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P46" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R46" t="n">
+      <c r="V46" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W46" t="n">
         <v>1.33</v>
       </c>
-      <c r="S46" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.2</v>
-      </c>
       <c r="X46" t="n">
-        <v>3.88</v>
+        <v>3.3</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.61</v>
+        <v>1.98</v>
       </c>
       <c r="Z46" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC46" t="n">
         <v>2.05</v>
       </c>
-      <c r="AA46" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AD46" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3']</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '10']</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AJ46" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45755.89583333334</v>
@@ -6448,25 +6448,25 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -6474,83 +6474,83 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="M47" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="N47" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="O47" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="P47" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="R47" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X47" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH47" t="n">
         <v>2.75</v>
       </c>
-      <c r="T47" t="n">
-        <v>3</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X47" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>['3']</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>['7', '10']</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AI47" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AJ47" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45755.89583333334</v>
